--- a/fixtures/files/intelliplan_timmar_MBAB_2026-08.xlsx
+++ b/fixtures/files/intelliplan_timmar_MBAB_2026-08.xlsx
@@ -470,7 +470,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="E5" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="F5" s="1">
         <v>46235</v>
@@ -496,7 +496,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="E6" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="F6" t="str">
         <v>2/8 2026</v>
@@ -522,7 +522,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="E7" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="F7" s="1">
         <v>46237</v>
@@ -548,7 +548,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="E8" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="F8" s="1">
         <v>46238</v>
@@ -574,7 +574,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="E9" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="F9" s="1">
         <v>46243</v>
@@ -600,7 +600,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="E10" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="F10" s="1">
         <v>46245</v>
@@ -626,7 +626,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="E11" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="F11" s="1">
         <v>46246</v>
@@ -652,7 +652,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="E12" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="F12" s="1">
         <v>46251</v>
@@ -678,7 +678,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="E13" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="F13" t="str">
         <v>19/8 2026</v>
@@ -704,7 +704,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="E14" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="F14" s="1">
         <v>46255</v>
@@ -730,7 +730,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="E15" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="F15" s="1">
         <v>46256</v>
@@ -756,7 +756,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="E16" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="F16" t="str">
         <v>23/8 2026</v>
@@ -782,7 +782,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="E17" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="F17" s="1">
         <v>46263</v>
@@ -808,7 +808,7 @@
         <v>Alva Ali</v>
       </c>
       <c r="E18" t="str">
-        <v>19720821-1586</v>
+        <v>19720821-9837</v>
       </c>
       <c r="F18" t="str">
         <v>31/8 2026</v>
@@ -834,7 +834,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="E19" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="F19" t="str">
         <v>3/8 2026</v>
@@ -860,7 +860,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="E20" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="F20" s="1">
         <v>46238</v>
@@ -886,7 +886,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="E21" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="F21" s="1">
         <v>46240</v>
@@ -912,7 +912,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="E22" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="F22" s="1">
         <v>46241</v>
@@ -938,7 +938,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="E23" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="F23" s="1">
         <v>46246</v>
@@ -964,7 +964,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="E24" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="F24" t="str">
         <v>2026-08-19</v>
@@ -990,7 +990,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="E25" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="F25" s="1">
         <v>46259</v>
@@ -1016,7 +1016,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="E26" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="F26" s="1">
         <v>46260</v>
@@ -1042,7 +1042,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="E27" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="F27" t="str">
         <v>27/8 2026</v>
@@ -1068,7 +1068,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="E28" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="F28" s="1">
         <v>46264</v>
@@ -1094,7 +1094,7 @@
         <v>Agnes Hussein</v>
       </c>
       <c r="E29" t="str">
-        <v>19641028-6360</v>
+        <v>19641028-9927</v>
       </c>
       <c r="F29" s="1">
         <v>46265</v>
@@ -1120,7 +1120,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="E30" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="F30" s="1">
         <v>46235</v>
@@ -1146,7 +1146,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="E31" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="F31" t="str">
         <v>2026-08-04</v>
@@ -1172,7 +1172,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="E32" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="F32" t="str">
         <v>2026-08-06</v>
@@ -1198,7 +1198,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="E33" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="F33" s="1">
         <v>46254</v>
@@ -1224,7 +1224,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="E34" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="F34" s="1">
         <v>46256</v>
@@ -1250,7 +1250,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="E35" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="F35" t="str">
         <v>26/8 2026</v>
@@ -1276,7 +1276,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="E36" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="F36" s="1">
         <v>46262</v>
@@ -1302,7 +1302,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="E37" t="str">
-        <v>19650618-7332</v>
+        <v>19650618-9940</v>
       </c>
       <c r="F37" t="str">
         <v>29/8 2026</v>
@@ -1328,7 +1328,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="E38" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="F38" s="1">
         <v>46236</v>
@@ -1354,7 +1354,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="E39" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="F39" s="1">
         <v>46238</v>
@@ -1380,7 +1380,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="E40" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="F40" s="1">
         <v>46242</v>
@@ -1406,7 +1406,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="E41" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="F41" t="str">
         <v>16/8 2026</v>
@@ -1432,7 +1432,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="E42" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="F42" s="1">
         <v>46254</v>
@@ -1458,7 +1458,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="E43" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="F43" s="1">
         <v>46261</v>
@@ -1544,7 +1544,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="E47" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="F47" s="1">
         <v>46236</v>
@@ -1570,7 +1570,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="E48" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="F48" t="str">
         <v>8/8 2026</v>
@@ -1596,7 +1596,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="E49" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="F49" s="1">
         <v>46249</v>
@@ -1622,7 +1622,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="E50" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="F50" s="1">
         <v>46251</v>
@@ -1648,7 +1648,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="E51" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="F51" t="str">
         <v>18/8 2026</v>
@@ -1674,7 +1674,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="E52" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="F52" s="1">
         <v>46254</v>
@@ -1700,7 +1700,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="E53" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="F53" s="1">
         <v>46258</v>
@@ -1726,7 +1726,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="E54" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="F54" s="1">
         <v>46260</v>
@@ -1752,7 +1752,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="E55" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="F55" s="1">
         <v>46261</v>
@@ -1778,7 +1778,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="E56" t="str">
-        <v>20030629-8555</v>
+        <v>20030629-9975</v>
       </c>
       <c r="F56" t="str">
         <v>30/8 2026</v>
@@ -1804,7 +1804,7 @@
         <v>Maja Olsson</v>
       </c>
       <c r="E57" t="str">
-        <v>19901103-4783</v>
+        <v>19901103-9899</v>
       </c>
       <c r="F57" s="1">
         <v>46235</v>
@@ -1830,7 +1830,7 @@
         <v>Maja Olsson</v>
       </c>
       <c r="E58" t="str">
-        <v>19901103-4783</v>
+        <v>19901103-9899</v>
       </c>
       <c r="F58" s="1">
         <v>46238</v>
@@ -1856,7 +1856,7 @@
         <v>Maja Olsson</v>
       </c>
       <c r="E59" t="str">
-        <v>19901103-4783</v>
+        <v>19901103-9899</v>
       </c>
       <c r="F59" t="str">
         <v>5/8 2026</v>
@@ -1882,7 +1882,7 @@
         <v>Maja Olsson</v>
       </c>
       <c r="E60" t="str">
-        <v>19901103-4783</v>
+        <v>19901103-9899</v>
       </c>
       <c r="F60" s="1">
         <v>46243</v>
@@ -1908,7 +1908,7 @@
         <v>Maja Olsson</v>
       </c>
       <c r="E61" t="str">
-        <v>19901103-4783</v>
+        <v>19901103-9899</v>
       </c>
       <c r="F61" t="str">
         <v>14/8 2026</v>
@@ -1934,7 +1934,7 @@
         <v>Maja Olsson</v>
       </c>
       <c r="E62" t="str">
-        <v>19901103-4783</v>
+        <v>19901103-9899</v>
       </c>
       <c r="F62" s="1">
         <v>46253</v>
@@ -1960,7 +1960,7 @@
         <v>Maja Olsson</v>
       </c>
       <c r="E63" t="str">
-        <v>19901103-4783</v>
+        <v>19901103-9899</v>
       </c>
       <c r="F63" t="str">
         <v>2026-08-27</v>
@@ -1986,7 +1986,7 @@
         <v>Maja Olsson</v>
       </c>
       <c r="E64" t="str">
-        <v>19901103-4783</v>
+        <v>19901103-9899</v>
       </c>
       <c r="F64" t="str">
         <v>2026-08-28</v>
@@ -2012,7 +2012,7 @@
         <v>Maja Olsson</v>
       </c>
       <c r="E65" t="str">
-        <v>19901103-4783</v>
+        <v>19901103-9899</v>
       </c>
       <c r="F65" t="str">
         <v>30/8 2026</v>
@@ -2058,7 +2058,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="E68" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="F68" s="1">
         <v>46238</v>
@@ -2084,7 +2084,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="E69" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="F69" t="str">
         <v>5/8 2026</v>
@@ -2110,7 +2110,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="E70" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="F70" s="1">
         <v>46241</v>
@@ -2136,7 +2136,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="E71" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="F71" s="1">
         <v>46242</v>
@@ -2162,7 +2162,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="E72" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="F72" s="1">
         <v>46245</v>
@@ -2188,7 +2188,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="E73" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="F73" s="1">
         <v>46249</v>
@@ -2214,7 +2214,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="E74" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="F74" s="1">
         <v>46250</v>
@@ -2240,7 +2240,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="E75" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="F75" t="str">
         <v>17/8 2026</v>
@@ -2266,7 +2266,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="E76" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="F76" t="str">
         <v>2026-08-23</v>
@@ -2292,7 +2292,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="E77" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="F77" s="1">
         <v>46258</v>
@@ -2318,7 +2318,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="E78" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="F78" t="str">
         <v>25/8 2026</v>
@@ -2344,7 +2344,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="E79" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="F79" s="1">
         <v>46260</v>
@@ -2370,7 +2370,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="E80" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="F80" s="1">
         <v>46264</v>
@@ -2396,7 +2396,7 @@
         <v>Ida Abdullahi</v>
       </c>
       <c r="E81" t="str">
-        <v>20050703-0666</v>
+        <v>20050703-9816</v>
       </c>
       <c r="F81" s="1">
         <v>46265</v>
@@ -2422,7 +2422,7 @@
         <v>Viktor Danielsson</v>
       </c>
       <c r="E82" t="str">
-        <v>19851220-3939</v>
+        <v>19851220-9878</v>
       </c>
       <c r="F82" s="1">
         <v>46238</v>
@@ -2448,7 +2448,7 @@
         <v>Viktor Danielsson</v>
       </c>
       <c r="E83" t="str">
-        <v>19851220-3939</v>
+        <v>19851220-9878</v>
       </c>
       <c r="F83" s="1">
         <v>46241</v>
@@ -2474,7 +2474,7 @@
         <v>Viktor Danielsson</v>
       </c>
       <c r="E84" t="str">
-        <v>19851220-3939</v>
+        <v>19851220-9878</v>
       </c>
       <c r="F84" s="1">
         <v>46246</v>
@@ -2500,7 +2500,7 @@
         <v>Viktor Danielsson</v>
       </c>
       <c r="E85" t="str">
-        <v>19851220-3939</v>
+        <v>19851220-9878</v>
       </c>
       <c r="F85" s="1">
         <v>46249</v>
@@ -2526,7 +2526,7 @@
         <v>Viktor Danielsson</v>
       </c>
       <c r="E86" t="str">
-        <v>19851220-3939</v>
+        <v>19851220-9878</v>
       </c>
       <c r="F86" t="str">
         <v>2026-08-19</v>
@@ -2552,7 +2552,7 @@
         <v>Viktor Danielsson</v>
       </c>
       <c r="E87" t="str">
-        <v>19851220-3939</v>
+        <v>19851220-9878</v>
       </c>
       <c r="F87" t="str">
         <v>2026-08-24</v>
@@ -2578,7 +2578,7 @@
         <v>Viktor Danielsson</v>
       </c>
       <c r="E88" t="str">
-        <v>19851220-3939</v>
+        <v>19851220-9878</v>
       </c>
       <c r="F88" s="1">
         <v>46262</v>
@@ -2604,7 +2604,7 @@
         <v>Viktor Danielsson</v>
       </c>
       <c r="E89" t="str">
-        <v>19851220-3939</v>
+        <v>19851220-9878</v>
       </c>
       <c r="F89" t="str">
         <v>2026-08-29</v>
@@ -2630,7 +2630,7 @@
         <v>Viktor Danielsson</v>
       </c>
       <c r="E90" t="str">
-        <v>19851220-3939</v>
+        <v>19851220-9878</v>
       </c>
       <c r="F90" s="1">
         <v>46264</v>
@@ -2656,7 +2656,7 @@
         <v>Viktor Danielsson</v>
       </c>
       <c r="E91" t="str">
-        <v>19851220-3939</v>
+        <v>19851220-9878</v>
       </c>
       <c r="F91" s="1">
         <v>46265</v>
@@ -2682,7 +2682,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="E92" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="F92" t="str">
         <v>4/8 2026</v>
@@ -2708,7 +2708,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="E93" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="F93" s="1">
         <v>46241</v>
@@ -2734,7 +2734,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="E94" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="F94" s="1">
         <v>46242</v>
@@ -2760,7 +2760,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="E95" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="F95" s="1">
         <v>46245</v>
@@ -2786,7 +2786,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="E96" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="F96" s="1">
         <v>46248</v>
@@ -2812,7 +2812,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="E97" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="F97" s="1">
         <v>46249</v>
@@ -2838,7 +2838,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="E98" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="F98" s="1">
         <v>46250</v>
@@ -2864,7 +2864,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="E99" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="F99" t="str">
         <v>18/8 2026</v>
@@ -2890,7 +2890,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="E100" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="F100" t="str">
         <v>2026-08-20</v>
@@ -2916,7 +2916,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="E101" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="F101" s="1">
         <v>46264</v>
@@ -2942,7 +2942,7 @@
         <v>Oskar Gustafsson</v>
       </c>
       <c r="E102" t="str">
-        <v>19861002-3270</v>
+        <v>19861002-9863</v>
       </c>
       <c r="F102" s="1">
         <v>46265</v>
@@ -2968,7 +2968,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="E103" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="F103" t="str">
         <v>13/8 2026</v>
@@ -2994,7 +2994,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="E104" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="F104" t="str">
         <v>17/8 2026</v>
@@ -3020,7 +3020,7 @@
         <v>Omar Magnusson</v>
       </c>
       <c r="E105" t="str">
-        <v>19970414-8171</v>
+        <v>19970414-9963</v>
       </c>
       <c r="F105" s="1">
         <v>46236</v>
@@ -3046,7 +3046,7 @@
         <v>Omar Magnusson</v>
       </c>
       <c r="E106" t="str">
-        <v>19970414-8171</v>
+        <v>19970414-9963</v>
       </c>
       <c r="F106" s="1">
         <v>46239</v>
@@ -3072,7 +3072,7 @@
         <v>Omar Magnusson</v>
       </c>
       <c r="E107" t="str">
-        <v>19970414-8171</v>
+        <v>19970414-9963</v>
       </c>
       <c r="F107" t="str">
         <v>2026-08-13</v>
@@ -3098,7 +3098,7 @@
         <v>Omar Magnusson</v>
       </c>
       <c r="E108" t="str">
-        <v>19970414-8171</v>
+        <v>19970414-9963</v>
       </c>
       <c r="F108" s="1">
         <v>46248</v>
@@ -3124,7 +3124,7 @@
         <v>Omar Magnusson</v>
       </c>
       <c r="E109" t="str">
-        <v>19970414-8171</v>
+        <v>19970414-9963</v>
       </c>
       <c r="F109" s="1">
         <v>46251</v>
@@ -3150,7 +3150,7 @@
         <v>Omar Magnusson</v>
       </c>
       <c r="E110" t="str">
-        <v>19970414-8171</v>
+        <v>19970414-9963</v>
       </c>
       <c r="F110" t="str">
         <v>20/8 2026</v>
@@ -3176,7 +3176,7 @@
         <v>Omar Magnusson</v>
       </c>
       <c r="E111" t="str">
-        <v>19970414-8171</v>
+        <v>19970414-9963</v>
       </c>
       <c r="F111" t="str">
         <v>22/8 2026</v>
@@ -3202,7 +3202,7 @@
         <v>Omar Magnusson</v>
       </c>
       <c r="E112" t="str">
-        <v>19970414-8171</v>
+        <v>19970414-9963</v>
       </c>
       <c r="F112" s="1">
         <v>46257</v>
@@ -3228,7 +3228,7 @@
         <v>Omar Magnusson</v>
       </c>
       <c r="E113" t="str">
-        <v>19970414-8171</v>
+        <v>19970414-9963</v>
       </c>
       <c r="F113" s="1">
         <v>46258</v>
@@ -3254,7 +3254,7 @@
         <v>Omar Magnusson</v>
       </c>
       <c r="E114" t="str">
-        <v>19970414-8171</v>
+        <v>19970414-9963</v>
       </c>
       <c r="F114" t="str">
         <v>29/8 2026</v>
@@ -3280,7 +3280,7 @@
         <v>Omar Magnusson</v>
       </c>
       <c r="E115" t="str">
-        <v>19970414-8171</v>
+        <v>19970414-9963</v>
       </c>
       <c r="F115" s="1">
         <v>46265</v>
@@ -3306,7 +3306,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="E116" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="F116" s="1">
         <v>46237</v>
@@ -3332,7 +3332,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="E117" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="F117" s="1">
         <v>46240</v>
@@ -3358,7 +3358,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="E118" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="F118" t="str">
         <v>2026-08-07</v>
@@ -3384,7 +3384,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="E119" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="F119" s="1">
         <v>46242</v>
@@ -3410,7 +3410,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="E120" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="F120" t="str">
         <v>10/8 2026</v>
@@ -3436,7 +3436,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="E121" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="F121" t="str">
         <v>11/8 2026</v>
@@ -3462,7 +3462,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="E122" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="F122" s="1">
         <v>46249</v>
@@ -3488,7 +3488,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="E123" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="F123" t="str">
         <v>16/8 2026</v>
@@ -3514,7 +3514,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="E124" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="F124" t="str">
         <v>20/8 2026</v>
@@ -3540,7 +3540,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="E125" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="F125" t="str">
         <v>2026-08-21</v>
@@ -3566,7 +3566,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="E126" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="F126" s="1">
         <v>46257</v>
@@ -3592,7 +3592,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="E127" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="F127" t="str">
         <v>24/8 2026</v>
@@ -3618,7 +3618,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="E128" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="F128" s="1">
         <v>46263</v>
@@ -3644,7 +3644,7 @@
         <v>Tilda Magnusson</v>
       </c>
       <c r="E129" t="str">
-        <v>19700218-6612</v>
+        <v>19700218-9939</v>
       </c>
       <c r="F129" s="1">
         <v>46264</v>
@@ -3670,7 +3670,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="E130" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="F130" s="1">
         <v>46241</v>
@@ -3696,7 +3696,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="E131" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="F131" t="str">
         <v>9/8 2026</v>
@@ -3722,7 +3722,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="E132" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="F132" s="1">
         <v>46247</v>
@@ -3748,7 +3748,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="E133" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="F133" s="1">
         <v>46250</v>
@@ -3774,7 +3774,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="E134" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="F134" s="1">
         <v>46254</v>
@@ -3800,7 +3800,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="E135" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="F135" s="1">
         <v>46259</v>
@@ -3826,7 +3826,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="E136" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="F136" s="1">
         <v>46263</v>
@@ -3852,7 +3852,7 @@
         <v>Ali Mohamed</v>
       </c>
       <c r="E137" t="str">
-        <v>19700223-1483</v>
+        <v>19700223-9825</v>
       </c>
       <c r="F137" t="str">
         <v>1/8 2026</v>
@@ -3878,7 +3878,7 @@
         <v>Ali Mohamed</v>
       </c>
       <c r="E138" t="str">
-        <v>19700223-1483</v>
+        <v>19700223-9825</v>
       </c>
       <c r="F138" s="1">
         <v>46237</v>
@@ -3904,7 +3904,7 @@
         <v>Ali Mohamed</v>
       </c>
       <c r="E139" t="str">
-        <v>19700223-1483</v>
+        <v>19700223-9825</v>
       </c>
       <c r="F139" s="1">
         <v>46244</v>
@@ -3930,7 +3930,7 @@
         <v>Ali Mohamed</v>
       </c>
       <c r="E140" t="str">
-        <v>19700223-1483</v>
+        <v>19700223-9825</v>
       </c>
       <c r="F140" t="str">
         <v>29/8 2026</v>
@@ -3956,7 +3956,7 @@
         <v>Ali Mohamed</v>
       </c>
       <c r="E141" t="str">
-        <v>19700223-1483</v>
+        <v>19700223-9825</v>
       </c>
       <c r="F141" t="str">
         <v>30/8 2026</v>
@@ -3982,7 +3982,7 @@
         <v>Ali Mohamed</v>
       </c>
       <c r="E142" t="str">
-        <v>19700223-1483</v>
+        <v>19700223-9825</v>
       </c>
       <c r="F142" s="1">
         <v>46265</v>
@@ -4008,7 +4008,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="E143" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="F143" t="str">
         <v>1/8 2026</v>
@@ -4034,7 +4034,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="E144" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="F144" s="1">
         <v>46237</v>
@@ -4060,7 +4060,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="E145" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="F145" t="str">
         <v>5/8 2026</v>
@@ -4086,7 +4086,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="E146" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="F146" t="str">
         <v>2026-08-12</v>
@@ -4112,7 +4112,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="E147" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="F147" s="1">
         <v>46248</v>
@@ -4138,7 +4138,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="E148" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="F148" s="1">
         <v>46256</v>
@@ -4164,7 +4164,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="E149" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="F149" s="1">
         <v>46262</v>
@@ -4190,7 +4190,7 @@
         <v>Mariam Nyström</v>
       </c>
       <c r="E150" t="str">
-        <v>19971110-1684</v>
+        <v>19971110-9836</v>
       </c>
       <c r="F150" s="1">
         <v>46265</v>
@@ -4216,7 +4216,7 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="E151" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="F151" s="1">
         <v>46240</v>
@@ -4242,7 +4242,7 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="E152" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="F152" t="str">
         <v>15/8 2026</v>
@@ -4268,7 +4268,7 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="E153" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="F153" t="str">
         <v>23/8 2026</v>
@@ -4294,7 +4294,7 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="E154" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="F154" s="1">
         <v>46265</v>
@@ -4320,7 +4320,7 @@
         <v>Noor Sjöberg</v>
       </c>
       <c r="E155" t="str">
-        <v>19960615-5118</v>
+        <v>19960615-9904</v>
       </c>
       <c r="F155" s="1">
         <v>46236</v>
@@ -4346,7 +4346,7 @@
         <v>Noor Sjöberg</v>
       </c>
       <c r="E156" t="str">
-        <v>19960615-5118</v>
+        <v>19960615-9904</v>
       </c>
       <c r="F156" s="1">
         <v>46238</v>
@@ -4372,7 +4372,7 @@
         <v>Noor Sjöberg</v>
       </c>
       <c r="E157" t="str">
-        <v>19960615-5118</v>
+        <v>19960615-9904</v>
       </c>
       <c r="F157" t="str">
         <v>5/8 2026</v>
@@ -4398,7 +4398,7 @@
         <v>Noor Sjöberg</v>
       </c>
       <c r="E158" t="str">
-        <v>19960615-5118</v>
+        <v>19960615-9904</v>
       </c>
       <c r="F158" s="1">
         <v>46249</v>
@@ -4424,7 +4424,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="E159" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="F159" s="1">
         <v>46235</v>
@@ -4450,7 +4450,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="E160" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="F160" s="1">
         <v>46237</v>
@@ -4476,7 +4476,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="E161" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="F161" s="1">
         <v>46239</v>
@@ -4502,7 +4502,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="E162" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="F162" s="1">
         <v>46242</v>
@@ -4528,7 +4528,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="E163" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="F163" s="1">
         <v>46245</v>
@@ -4554,7 +4554,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="E164" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="F164" s="1">
         <v>46246</v>
@@ -4580,7 +4580,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="E165" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="F165" t="str">
         <v>13/8 2026</v>
@@ -4606,7 +4606,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="E166" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="F166" s="1">
         <v>46250</v>
@@ -4632,7 +4632,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="E167" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="F167" s="1">
         <v>46251</v>
@@ -4658,7 +4658,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="E168" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="F168" t="str">
         <v>18/8 2026</v>
@@ -4684,7 +4684,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="E169" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="F169" s="1">
         <v>46257</v>
@@ -4710,7 +4710,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="E170" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="F170" s="1">
         <v>46264</v>
@@ -4736,7 +4736,7 @@
         <v>Emil Ström</v>
       </c>
       <c r="E171" t="str">
-        <v>19740725-5244</v>
+        <v>19740725-9907</v>
       </c>
       <c r="F171" s="1">
         <v>46265</v>
@@ -4762,7 +4762,7 @@
         <v>Ebba Svensson</v>
       </c>
       <c r="E172" t="str">
-        <v>19780312-9662</v>
+        <v>19780312-9993</v>
       </c>
       <c r="F172" s="1">
         <v>46235</v>
@@ -4788,7 +4788,7 @@
         <v>Ebba Svensson</v>
       </c>
       <c r="E173" t="str">
-        <v>19780312-9662</v>
+        <v>19780312-9993</v>
       </c>
       <c r="F173" s="1">
         <v>46236</v>
@@ -4814,7 +4814,7 @@
         <v>Ebba Svensson</v>
       </c>
       <c r="E174" t="str">
-        <v>19780312-9662</v>
+        <v>19780312-9993</v>
       </c>
       <c r="F174" t="str">
         <v>3/8 2026</v>
@@ -4840,7 +4840,7 @@
         <v>Ebba Svensson</v>
       </c>
       <c r="E175" t="str">
-        <v>19780312-9662</v>
+        <v>19780312-9993</v>
       </c>
       <c r="F175" t="str">
         <v>2026-08-04</v>
@@ -4866,7 +4866,7 @@
         <v>Ebba Svensson</v>
       </c>
       <c r="E176" t="str">
-        <v>19780312-9662</v>
+        <v>19780312-9993</v>
       </c>
       <c r="F176" t="str">
         <v>5/8 2026</v>
@@ -4892,7 +4892,7 @@
         <v>Ebba Svensson</v>
       </c>
       <c r="E177" t="str">
-        <v>19780312-9662</v>
+        <v>19780312-9993</v>
       </c>
       <c r="F177" s="1">
         <v>46240</v>
@@ -4918,7 +4918,7 @@
         <v>Ebba Svensson</v>
       </c>
       <c r="E178" t="str">
-        <v>19780312-9662</v>
+        <v>19780312-9993</v>
       </c>
       <c r="F178" s="1">
         <v>46241</v>
@@ -4944,7 +4944,7 @@
         <v>Ebba Svensson</v>
       </c>
       <c r="E179" t="str">
-        <v>19780312-9662</v>
+        <v>19780312-9993</v>
       </c>
       <c r="F179" s="1">
         <v>46242</v>
@@ -4970,7 +4970,7 @@
         <v>Ebba Svensson</v>
       </c>
       <c r="E180" t="str">
-        <v>19780312-9662</v>
+        <v>19780312-9993</v>
       </c>
       <c r="F180" s="1">
         <v>46243</v>
@@ -4996,7 +4996,7 @@
         <v>Ebba Svensson</v>
       </c>
       <c r="E181" t="str">
-        <v>19780312-9662</v>
+        <v>19780312-9993</v>
       </c>
       <c r="F181" s="1">
         <v>46244</v>
@@ -5022,7 +5022,7 @@
         <v>Ebba Svensson</v>
       </c>
       <c r="E182" t="str">
-        <v>19780312-9662</v>
+        <v>19780312-9993</v>
       </c>
       <c r="F182" t="str">
         <v>2026-08-11</v>
@@ -5048,7 +5048,7 @@
         <v>Ebba Svensson</v>
       </c>
       <c r="E183" t="str">
-        <v>19780312-9662</v>
+        <v>19780312-9993</v>
       </c>
       <c r="F183" s="1">
         <v>46246</v>
@@ -5074,7 +5074,7 @@
         <v>Ebba Svensson</v>
       </c>
       <c r="E184" t="str">
-        <v>19780312-9662</v>
+        <v>19780312-9993</v>
       </c>
       <c r="F184" s="1">
         <v>46247</v>
@@ -5100,7 +5100,7 @@
         <v>Ebba Svensson</v>
       </c>
       <c r="E185" t="str">
-        <v>19780312-9662</v>
+        <v>19780312-9993</v>
       </c>
       <c r="F185" s="1">
         <v>46248</v>
@@ -5166,7 +5166,7 @@
         <v>Gustav Danielsson</v>
       </c>
       <c r="E189" t="str">
-        <v>19950224-2242</v>
+        <v>19950224-9841</v>
       </c>
       <c r="F189" s="1">
         <v>46243</v>
@@ -5192,7 +5192,7 @@
         <v>Gustav Danielsson</v>
       </c>
       <c r="E190" t="str">
-        <v>19950224-2242</v>
+        <v>19950224-9841</v>
       </c>
       <c r="F190" s="1">
         <v>46247</v>
@@ -5218,7 +5218,7 @@
         <v>Gustav Danielsson</v>
       </c>
       <c r="E191" t="str">
-        <v>19950224-2242</v>
+        <v>19950224-9841</v>
       </c>
       <c r="F191" t="str">
         <v>2026-08-22</v>
@@ -5244,7 +5244,7 @@
         <v>Gustav Danielsson</v>
       </c>
       <c r="E192" t="str">
-        <v>19950224-2242</v>
+        <v>19950224-9841</v>
       </c>
       <c r="F192" s="1">
         <v>46261</v>
@@ -5270,7 +5270,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="E193" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="F193" s="1">
         <v>46237</v>
@@ -5296,7 +5296,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="E194" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="F194" s="1">
         <v>46241</v>
@@ -5322,7 +5322,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="E195" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="F195" s="1">
         <v>46244</v>
@@ -5348,7 +5348,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="E196" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="F196" s="1">
         <v>46250</v>
@@ -5374,7 +5374,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="E197" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="F197" s="1">
         <v>46252</v>
@@ -5400,7 +5400,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="E198" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="F198" t="str">
         <v>21/8 2026</v>
@@ -5426,7 +5426,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="E199" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="F199" s="1">
         <v>46261</v>
@@ -5452,7 +5452,7 @@
         <v>Adam Gustafsson</v>
       </c>
       <c r="E200" t="str">
-        <v>19731122-9103</v>
+        <v>19731122-9988</v>
       </c>
       <c r="F200" t="str">
         <v>28/8 2026</v>
@@ -5478,7 +5478,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="E201" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="F201" s="1">
         <v>46235</v>
@@ -5504,7 +5504,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="E202" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="F202" t="str">
         <v>5/8 2026</v>
@@ -5530,7 +5530,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="E203" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="F203" s="1">
         <v>46240</v>
@@ -5556,7 +5556,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="E204" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="F204" t="str">
         <v>7/8 2026</v>
@@ -5582,7 +5582,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="E205" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="F205" s="1">
         <v>46242</v>
@@ -5608,7 +5608,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="E206" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="F206" s="1">
         <v>46243</v>
@@ -5634,7 +5634,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="E207" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="F207" s="1">
         <v>46247</v>
@@ -5660,7 +5660,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="E208" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="F208" s="1">
         <v>46252</v>
@@ -5686,7 +5686,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="E209" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="F209" s="1">
         <v>46253</v>
@@ -5712,7 +5712,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="E210" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="F210" s="1">
         <v>46255</v>
@@ -5738,7 +5738,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="E211" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="F211" s="1">
         <v>46257</v>
@@ -5764,7 +5764,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="E212" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="F212" t="str">
         <v>2026-08-26</v>
@@ -5790,7 +5790,7 @@
         <v>Lucas Lundin</v>
       </c>
       <c r="E213" t="str">
-        <v>19910501-4154</v>
+        <v>19910501-9880</v>
       </c>
       <c r="F213" s="1">
         <v>46265</v>
@@ -5816,7 +5816,7 @@
         <v>Noor Mohamed</v>
       </c>
       <c r="E214" t="str">
-        <v>19650307-0259</v>
+        <v>19650307-9805</v>
       </c>
       <c r="F214" t="str">
         <v>1/8 2026</v>
@@ -5842,7 +5842,7 @@
         <v>Noor Mohamed</v>
       </c>
       <c r="E215" t="str">
-        <v>19650307-0259</v>
+        <v>19650307-9805</v>
       </c>
       <c r="F215" s="1">
         <v>46236</v>
@@ -5868,7 +5868,7 @@
         <v>Noor Mohamed</v>
       </c>
       <c r="E216" t="str">
-        <v>19650307-0259</v>
+        <v>19650307-9805</v>
       </c>
       <c r="F216" s="1">
         <v>46237</v>
@@ -5894,7 +5894,7 @@
         <v>Noor Mohamed</v>
       </c>
       <c r="E217" t="str">
-        <v>19650307-0259</v>
+        <v>19650307-9805</v>
       </c>
       <c r="F217" s="1">
         <v>46241</v>
@@ -5920,7 +5920,7 @@
         <v>Noor Mohamed</v>
       </c>
       <c r="E218" t="str">
-        <v>19650307-0259</v>
+        <v>19650307-9805</v>
       </c>
       <c r="F218" s="1">
         <v>46244</v>
@@ -5946,7 +5946,7 @@
         <v>Noor Mohamed</v>
       </c>
       <c r="E219" t="str">
-        <v>19650307-0259</v>
+        <v>19650307-9805</v>
       </c>
       <c r="F219" s="1">
         <v>46246</v>
@@ -5972,7 +5972,7 @@
         <v>Noor Mohamed</v>
       </c>
       <c r="E220" t="str">
-        <v>19650307-0259</v>
+        <v>19650307-9805</v>
       </c>
       <c r="F220" s="1">
         <v>46247</v>
@@ -5998,7 +5998,7 @@
         <v>Noor Mohamed</v>
       </c>
       <c r="E221" t="str">
-        <v>19650307-0259</v>
+        <v>19650307-9805</v>
       </c>
       <c r="F221" t="str">
         <v>2026-08-14</v>
@@ -6024,7 +6024,7 @@
         <v>Noor Mohamed</v>
       </c>
       <c r="E222" t="str">
-        <v>19650307-0259</v>
+        <v>19650307-9805</v>
       </c>
       <c r="F222" s="1">
         <v>46252</v>
@@ -6050,7 +6050,7 @@
         <v>Fatima Gustafsson</v>
       </c>
       <c r="E223" t="str">
-        <v>19911106-0159</v>
+        <v>19911106-9804</v>
       </c>
       <c r="F223" s="1">
         <v>46236</v>
@@ -6076,7 +6076,7 @@
         <v>Fatima Gustafsson</v>
       </c>
       <c r="E224" t="str">
-        <v>19911106-0159</v>
+        <v>19911106-9804</v>
       </c>
       <c r="F224" t="str">
         <v>7/8 2026</v>
@@ -6102,7 +6102,7 @@
         <v>Fatima Gustafsson</v>
       </c>
       <c r="E225" t="str">
-        <v>19911106-0159</v>
+        <v>19911106-9804</v>
       </c>
       <c r="F225" s="1">
         <v>46254</v>
@@ -6128,7 +6128,7 @@
         <v>Fatima Gustafsson</v>
       </c>
       <c r="E226" t="str">
-        <v>19911106-0159</v>
+        <v>19911106-9804</v>
       </c>
       <c r="F226" s="1">
         <v>46256</v>
@@ -6154,7 +6154,7 @@
         <v>Yusuf Jakobsson</v>
       </c>
       <c r="E227" t="str">
-        <v>19620308-9120</v>
+        <v>19620308-9989</v>
       </c>
       <c r="F227" t="str">
         <v>2026-08-01</v>
@@ -6180,7 +6180,7 @@
         <v>Yusuf Jakobsson</v>
       </c>
       <c r="E228" t="str">
-        <v>19620308-9120</v>
+        <v>19620308-9989</v>
       </c>
       <c r="F228" s="1">
         <v>46237</v>
@@ -6206,7 +6206,7 @@
         <v>Yusuf Jakobsson</v>
       </c>
       <c r="E229" t="str">
-        <v>19620308-9120</v>
+        <v>19620308-9989</v>
       </c>
       <c r="F229" s="1">
         <v>46238</v>
@@ -6232,7 +6232,7 @@
         <v>Yusuf Jakobsson</v>
       </c>
       <c r="E230" t="str">
-        <v>19620308-9120</v>
+        <v>19620308-9989</v>
       </c>
       <c r="F230" t="str">
         <v>7/8 2026</v>
@@ -6258,7 +6258,7 @@
         <v>Yusuf Jakobsson</v>
       </c>
       <c r="E231" t="str">
-        <v>19620308-9120</v>
+        <v>19620308-9989</v>
       </c>
       <c r="F231" s="1">
         <v>46250</v>
@@ -6284,7 +6284,7 @@
         <v>Yusuf Jakobsson</v>
       </c>
       <c r="E232" t="str">
-        <v>19620308-9120</v>
+        <v>19620308-9989</v>
       </c>
       <c r="F232" t="str">
         <v>2026-08-17</v>
@@ -6310,7 +6310,7 @@
         <v>Yusuf Jakobsson</v>
       </c>
       <c r="E233" t="str">
-        <v>19620308-9120</v>
+        <v>19620308-9989</v>
       </c>
       <c r="F233" t="str">
         <v>19/8 2026</v>
@@ -6336,7 +6336,7 @@
         <v>Yusuf Jakobsson</v>
       </c>
       <c r="E234" t="str">
-        <v>19620308-9120</v>
+        <v>19620308-9989</v>
       </c>
       <c r="F234" s="1">
         <v>46256</v>
@@ -6362,7 +6362,7 @@
         <v>Yusuf Jakobsson</v>
       </c>
       <c r="E235" t="str">
-        <v>19620308-9120</v>
+        <v>19620308-9989</v>
       </c>
       <c r="F235" s="1">
         <v>46257</v>
@@ -6388,7 +6388,7 @@
         <v>Yusuf Jakobsson</v>
       </c>
       <c r="E236" t="str">
-        <v>19620308-9120</v>
+        <v>19620308-9989</v>
       </c>
       <c r="F236" t="str">
         <v>26/8 2026</v>
@@ -6414,7 +6414,7 @@
         <v>Yusuf Jakobsson</v>
       </c>
       <c r="E237" t="str">
-        <v>19620308-9120</v>
+        <v>19620308-9989</v>
       </c>
       <c r="F237" s="1">
         <v>46262</v>
@@ -6440,7 +6440,7 @@
         <v>Yusuf Jakobsson</v>
       </c>
       <c r="E238" t="str">
-        <v>19620308-9120</v>
+        <v>19620308-9989</v>
       </c>
       <c r="F238" s="1">
         <v>46263</v>
@@ -6466,7 +6466,7 @@
         <v>Yusuf Jakobsson</v>
       </c>
       <c r="E239" t="str">
-        <v>19620308-9120</v>
+        <v>19620308-9989</v>
       </c>
       <c r="F239" t="str">
         <v>30/8 2026</v>
@@ -6492,7 +6492,7 @@
         <v>Yusuf Jakobsson</v>
       </c>
       <c r="E240" t="str">
-        <v>19620308-9120</v>
+        <v>19620308-9989</v>
       </c>
       <c r="F240" t="str">
         <v>2026-08-31</v>
@@ -6518,7 +6518,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="E241" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="F241" s="1">
         <v>46245</v>
@@ -6544,7 +6544,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="E242" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="F242" s="1">
         <v>46246</v>
@@ -6570,7 +6570,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="E243" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="F243" t="str">
         <v>2026-08-14</v>
@@ -6596,7 +6596,7 @@
         <v>Tilda Mattsson</v>
       </c>
       <c r="E244" t="str">
-        <v>19670817-4674</v>
+        <v>19670817-9897</v>
       </c>
       <c r="F244" t="str">
         <v>2026-08-22</v>
@@ -6622,7 +6622,7 @@
         <v>Freja Sandberg</v>
       </c>
       <c r="E245" t="str">
-        <v>19731011-0114</v>
+        <v>19731011-9800</v>
       </c>
       <c r="F245" s="1">
         <v>46236</v>
@@ -6648,7 +6648,7 @@
         <v>Freja Sandberg</v>
       </c>
       <c r="E246" t="str">
-        <v>19731011-0114</v>
+        <v>19731011-9800</v>
       </c>
       <c r="F246" t="str">
         <v>3/8 2026</v>
@@ -6674,7 +6674,7 @@
         <v>Freja Sandberg</v>
       </c>
       <c r="E247" t="str">
-        <v>19731011-0114</v>
+        <v>19731011-9800</v>
       </c>
       <c r="F247" s="1">
         <v>46240</v>
@@ -6700,7 +6700,7 @@
         <v>Freja Sandberg</v>
       </c>
       <c r="E248" t="str">
-        <v>19731011-0114</v>
+        <v>19731011-9800</v>
       </c>
       <c r="F248" t="str">
         <v>7/8 2026</v>
@@ -6726,7 +6726,7 @@
         <v>Freja Sandberg</v>
       </c>
       <c r="E249" t="str">
-        <v>19731011-0114</v>
+        <v>19731011-9800</v>
       </c>
       <c r="F249" s="1">
         <v>46245</v>
@@ -6752,7 +6752,7 @@
         <v>Freja Sandberg</v>
       </c>
       <c r="E250" t="str">
-        <v>19731011-0114</v>
+        <v>19731011-9800</v>
       </c>
       <c r="F250" s="1">
         <v>46250</v>
@@ -6778,7 +6778,7 @@
         <v>Freja Sandberg</v>
       </c>
       <c r="E251" t="str">
-        <v>19731011-0114</v>
+        <v>19731011-9800</v>
       </c>
       <c r="F251" s="1">
         <v>46257</v>
@@ -6804,7 +6804,7 @@
         <v>Freja Sandberg</v>
       </c>
       <c r="E252" t="str">
-        <v>19731011-0114</v>
+        <v>19731011-9800</v>
       </c>
       <c r="F252" s="1">
         <v>46258</v>
@@ -6830,7 +6830,7 @@
         <v>Freja Sandberg</v>
       </c>
       <c r="E253" t="str">
-        <v>19731011-0114</v>
+        <v>19731011-9800</v>
       </c>
       <c r="F253" t="str">
         <v>26/8 2026</v>
@@ -6856,7 +6856,7 @@
         <v>Freja Sandberg</v>
       </c>
       <c r="E254" t="str">
-        <v>19731011-0114</v>
+        <v>19731011-9800</v>
       </c>
       <c r="F254" s="1">
         <v>46262</v>
@@ -6882,7 +6882,7 @@
         <v>Ludvig Larsson</v>
       </c>
       <c r="E256" t="str">
-        <v>19961117-0607</v>
+        <v>19961117-9814</v>
       </c>
       <c r="F256" t="str">
         <v>6/8 2026</v>
@@ -6908,7 +6908,7 @@
         <v>Ludvig Larsson</v>
       </c>
       <c r="E257" t="str">
-        <v>19961117-0607</v>
+        <v>19961117-9814</v>
       </c>
       <c r="F257" s="1">
         <v>46247</v>
@@ -6934,7 +6934,7 @@
         <v>Ludvig Larsson</v>
       </c>
       <c r="E258" t="str">
-        <v>19961117-0607</v>
+        <v>19961117-9814</v>
       </c>
       <c r="F258" s="1">
         <v>46248</v>
@@ -6960,7 +6960,7 @@
         <v>Ludvig Larsson</v>
       </c>
       <c r="E259" t="str">
-        <v>19961117-0607</v>
+        <v>19961117-9814</v>
       </c>
       <c r="F259" t="str">
         <v>16/8 2026</v>
@@ -6986,7 +6986,7 @@
         <v>Ludvig Larsson</v>
       </c>
       <c r="E260" t="str">
-        <v>19961117-0607</v>
+        <v>19961117-9814</v>
       </c>
       <c r="F260" s="1">
         <v>46257</v>
@@ -7012,7 +7012,7 @@
         <v>Ludvig Larsson</v>
       </c>
       <c r="E261" t="str">
-        <v>19961117-0607</v>
+        <v>19961117-9814</v>
       </c>
       <c r="F261" t="str">
         <v>24/8 2026</v>
@@ -7038,7 +7038,7 @@
         <v>Anna Nyström</v>
       </c>
       <c r="E262" t="str">
-        <v>19650916-1524</v>
+        <v>19650916-9832</v>
       </c>
       <c r="F262" t="str">
         <v>2026-08-04</v>
@@ -7064,7 +7064,7 @@
         <v>Anna Nyström</v>
       </c>
       <c r="E263" t="str">
-        <v>19650916-1524</v>
+        <v>19650916-9832</v>
       </c>
       <c r="F263" s="1">
         <v>46242</v>
@@ -7090,7 +7090,7 @@
         <v>Anna Nyström</v>
       </c>
       <c r="E264" t="str">
-        <v>19650916-1524</v>
+        <v>19650916-9832</v>
       </c>
       <c r="F264" s="1">
         <v>46244</v>
@@ -7116,7 +7116,7 @@
         <v>Anna Nyström</v>
       </c>
       <c r="E265" t="str">
-        <v>19650916-1524</v>
+        <v>19650916-9832</v>
       </c>
       <c r="F265" t="str">
         <v>12/8 2026</v>
@@ -7142,7 +7142,7 @@
         <v>Anna Nyström</v>
       </c>
       <c r="E266" t="str">
-        <v>19650916-1524</v>
+        <v>19650916-9832</v>
       </c>
       <c r="F266" s="1">
         <v>46252</v>
@@ -7168,7 +7168,7 @@
         <v>Anna Nyström</v>
       </c>
       <c r="E267" t="str">
-        <v>19650916-1524</v>
+        <v>19650916-9832</v>
       </c>
       <c r="F267" s="1">
         <v>46256</v>
@@ -7194,7 +7194,7 @@
         <v>Anna Nyström</v>
       </c>
       <c r="E268" t="str">
-        <v>19650916-1524</v>
+        <v>19650916-9832</v>
       </c>
       <c r="F268" t="str">
         <v>24/8 2026</v>
@@ -7220,7 +7220,7 @@
         <v>Anna Nyström</v>
       </c>
       <c r="E269" t="str">
-        <v>19650916-1524</v>
+        <v>19650916-9832</v>
       </c>
       <c r="F269" s="1">
         <v>46263</v>
@@ -7246,7 +7246,7 @@
         <v>Anna Nyström</v>
       </c>
       <c r="E270" t="str">
-        <v>19650916-1524</v>
+        <v>19650916-9832</v>
       </c>
       <c r="F270" s="1">
         <v>46264</v>
@@ -7272,7 +7272,7 @@
         <v>Freja Sandberg</v>
       </c>
       <c r="E271" t="str">
-        <v>19731011-0114</v>
+        <v>19731011-9800</v>
       </c>
       <c r="F271" s="1">
         <v>46251</v>
@@ -7298,7 +7298,7 @@
         <v>Yusuf Ahmed</v>
       </c>
       <c r="E272" t="str">
-        <v>19791213-0122</v>
+        <v>19791213-9800</v>
       </c>
       <c r="F272" s="1">
         <v>46237</v>
@@ -7324,7 +7324,7 @@
         <v>Yusuf Ahmed</v>
       </c>
       <c r="E273" t="str">
-        <v>19791213-0122</v>
+        <v>19791213-9800</v>
       </c>
       <c r="F273" t="str">
         <v>10/8 2026</v>
@@ -7350,7 +7350,7 @@
         <v>Yusuf Ahmed</v>
       </c>
       <c r="E274" t="str">
-        <v>19791213-0122</v>
+        <v>19791213-9800</v>
       </c>
       <c r="F274" t="str">
         <v>2026-08-17</v>
@@ -7376,7 +7376,7 @@
         <v>Yusuf Ahmed</v>
       </c>
       <c r="E275" t="str">
-        <v>19791213-0122</v>
+        <v>19791213-9800</v>
       </c>
       <c r="F275" s="1">
         <v>46252</v>
@@ -7402,7 +7402,7 @@
         <v>Yusuf Ahmed</v>
       </c>
       <c r="E276" t="str">
-        <v>19791213-0122</v>
+        <v>19791213-9800</v>
       </c>
       <c r="F276" s="1">
         <v>46258</v>
@@ -7428,7 +7428,7 @@
         <v>Yusuf Ahmed</v>
       </c>
       <c r="E277" t="str">
-        <v>19791213-0122</v>
+        <v>19791213-9800</v>
       </c>
       <c r="F277" s="1">
         <v>46260</v>
@@ -7454,7 +7454,7 @@
         <v>Daniel Larsson</v>
       </c>
       <c r="E278" t="str">
-        <v>19700809-1402</v>
+        <v>19700809-9827</v>
       </c>
       <c r="F278" s="1">
         <v>46239</v>
@@ -7480,7 +7480,7 @@
         <v>Daniel Larsson</v>
       </c>
       <c r="E279" t="str">
-        <v>19700809-1402</v>
+        <v>19700809-9827</v>
       </c>
       <c r="F279" s="1">
         <v>46247</v>
@@ -7506,7 +7506,7 @@
         <v>Daniel Larsson</v>
       </c>
       <c r="E280" t="str">
-        <v>19700809-1402</v>
+        <v>19700809-9827</v>
       </c>
       <c r="F280" t="str">
         <v>2026-08-15</v>
@@ -7532,7 +7532,7 @@
         <v>Daniel Larsson</v>
       </c>
       <c r="E281" t="str">
-        <v>19700809-1402</v>
+        <v>19700809-9827</v>
       </c>
       <c r="F281" s="1">
         <v>46252</v>
@@ -7558,7 +7558,7 @@
         <v>Daniel Larsson</v>
       </c>
       <c r="E282" t="str">
-        <v>19700809-1402</v>
+        <v>19700809-9827</v>
       </c>
       <c r="F282" s="1">
         <v>46254</v>
@@ -7584,7 +7584,7 @@
         <v>Daniel Larsson</v>
       </c>
       <c r="E283" t="str">
-        <v>19700809-1402</v>
+        <v>19700809-9827</v>
       </c>
       <c r="F283" t="str">
         <v>2026-08-21</v>
@@ -7610,7 +7610,7 @@
         <v>Daniel Larsson</v>
       </c>
       <c r="E284" t="str">
-        <v>19700809-1402</v>
+        <v>19700809-9827</v>
       </c>
       <c r="F284" s="1">
         <v>46257</v>
@@ -7636,7 +7636,7 @@
         <v>Daniel Larsson</v>
       </c>
       <c r="E285" t="str">
-        <v>19700809-1402</v>
+        <v>19700809-9827</v>
       </c>
       <c r="F285" t="str">
         <v>24/8 2026</v>
@@ -7662,7 +7662,7 @@
         <v>Daniel Larsson</v>
       </c>
       <c r="E286" t="str">
-        <v>19700809-1402</v>
+        <v>19700809-9827</v>
       </c>
       <c r="F286" s="1">
         <v>46260</v>
@@ -7688,7 +7688,7 @@
         <v>Daniel Larsson</v>
       </c>
       <c r="E287" t="str">
-        <v>19700809-1402</v>
+        <v>19700809-9827</v>
       </c>
       <c r="F287" s="1">
         <v>46263</v>
@@ -7714,7 +7714,7 @@
         <v>Daniel Larsson</v>
       </c>
       <c r="E288" t="str">
-        <v>19700809-1402</v>
+        <v>19700809-9827</v>
       </c>
       <c r="F288" t="str">
         <v>31/8 2026</v>
@@ -7898,7 +7898,7 @@
         <v>Filip Lindström</v>
       </c>
       <c r="E298" t="str">
-        <v>19960907-8473</v>
+        <v>19960907-9968</v>
       </c>
       <c r="F298" s="1">
         <v>46250</v>
@@ -7924,7 +7924,7 @@
         <v>Filip Lindström</v>
       </c>
       <c r="E299" t="str">
-        <v>19960907-8473</v>
+        <v>19960907-9968</v>
       </c>
       <c r="F299" s="1">
         <v>46252</v>
@@ -7950,7 +7950,7 @@
         <v>Filip Lindström</v>
       </c>
       <c r="E300" t="str">
-        <v>19960907-8473</v>
+        <v>19960907-9968</v>
       </c>
       <c r="F300" s="1">
         <v>46255</v>
@@ -7976,7 +7976,7 @@
         <v>Filip Lindström</v>
       </c>
       <c r="E301" t="str">
-        <v>19960907-8473</v>
+        <v>19960907-9968</v>
       </c>
       <c r="F301" s="1">
         <v>46257</v>
@@ -8002,7 +8002,7 @@
         <v>Filip Lindström</v>
       </c>
       <c r="E302" t="str">
-        <v>19960907-8473</v>
+        <v>19960907-9968</v>
       </c>
       <c r="F302" s="1">
         <v>46258</v>
@@ -8028,7 +8028,7 @@
         <v>Filip Lindström</v>
       </c>
       <c r="E303" t="str">
-        <v>19960907-8473</v>
+        <v>19960907-9968</v>
       </c>
       <c r="F303" t="str">
         <v>25/8 2026</v>
@@ -8054,7 +8054,7 @@
         <v>Filip Lindström</v>
       </c>
       <c r="E304" t="str">
-        <v>19960907-8473</v>
+        <v>19960907-9968</v>
       </c>
       <c r="F304" s="1">
         <v>46260</v>
@@ -8080,7 +8080,7 @@
         <v>Filip Lindström</v>
       </c>
       <c r="E305" t="str">
-        <v>19960907-8473</v>
+        <v>19960907-9968</v>
       </c>
       <c r="F305" s="1">
         <v>46261</v>
@@ -8106,7 +8106,7 @@
         <v>Filip Lindström</v>
       </c>
       <c r="E306" t="str">
-        <v>19960907-8473</v>
+        <v>19960907-9968</v>
       </c>
       <c r="F306" t="str">
         <v>29/8 2026</v>
@@ -8132,7 +8132,7 @@
         <v>Filip Lindström</v>
       </c>
       <c r="E307" t="str">
-        <v>19960907-8473</v>
+        <v>19960907-9968</v>
       </c>
       <c r="F307" s="1">
         <v>46264</v>
@@ -8158,7 +8158,7 @@
         <v>Filip Lindström</v>
       </c>
       <c r="E308" t="str">
-        <v>19960907-8473</v>
+        <v>19960907-9968</v>
       </c>
       <c r="F308" s="1">
         <v>46265</v>
@@ -8184,7 +8184,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="E309" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="F309" s="1">
         <v>46238</v>
@@ -8210,7 +8210,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="E310" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="F310" t="str">
         <v>5/8 2026</v>
@@ -8236,7 +8236,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="E311" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="F311" s="1">
         <v>46244</v>
@@ -8262,7 +8262,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="E312" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="F312" s="1">
         <v>46250</v>
@@ -8288,7 +8288,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="E313" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="F313" t="str">
         <v>17/8 2026</v>
@@ -8314,7 +8314,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="E314" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="F314" s="1">
         <v>46258</v>
@@ -8340,7 +8340,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="E315" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="F315" t="str">
         <v>2026-08-26</v>
@@ -8366,7 +8366,7 @@
         <v>Oskar Pettersson</v>
       </c>
       <c r="E316" t="str">
-        <v>19800307-1373</v>
+        <v>19800307-9822</v>
       </c>
       <c r="F316" s="1">
         <v>46263</v>
@@ -8392,7 +8392,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="E317" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="F317" t="str">
         <v>2/8 2026</v>
@@ -8418,7 +8418,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="E318" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="F318" s="1">
         <v>46237</v>
@@ -8444,7 +8444,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="E319" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="F319" s="1">
         <v>46256</v>
@@ -8470,7 +8470,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="E320" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="F320" t="str">
         <v>24/8 2026</v>
@@ -8496,7 +8496,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="E321" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="F321" t="str">
         <v>2026-08-27</v>
@@ -8522,7 +8522,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="E322" t="str">
-        <v>19980105-8992</v>
+        <v>19980105-9974</v>
       </c>
       <c r="F322" s="1">
         <v>46264</v>
@@ -8548,7 +8548,7 @@
         <v>Nadia Danielsson</v>
       </c>
       <c r="E324" t="str">
-        <v>19800613-0036</v>
+        <v>19800613-9805</v>
       </c>
       <c r="F324" s="1">
         <v>46252</v>
@@ -8574,7 +8574,7 @@
         <v>Nadia Danielsson</v>
       </c>
       <c r="E325" t="str">
-        <v>19800613-0036</v>
+        <v>19800613-9805</v>
       </c>
       <c r="F325" t="str">
         <v>19/8 2026</v>
@@ -8600,7 +8600,7 @@
         <v>Nadia Danielsson</v>
       </c>
       <c r="E326" t="str">
-        <v>19800613-0036</v>
+        <v>19800613-9805</v>
       </c>
       <c r="F326" s="1">
         <v>46257</v>
@@ -8626,7 +8626,7 @@
         <v>Nadia Danielsson</v>
       </c>
       <c r="E327" t="str">
-        <v>19800613-0036</v>
+        <v>19800613-9805</v>
       </c>
       <c r="F327" s="1">
         <v>46258</v>
@@ -8652,7 +8652,7 @@
         <v>Nadia Danielsson</v>
       </c>
       <c r="E328" t="str">
-        <v>19800613-0036</v>
+        <v>19800613-9805</v>
       </c>
       <c r="F328" t="str">
         <v>25/8 2026</v>
@@ -8678,7 +8678,7 @@
         <v>Nadia Danielsson</v>
       </c>
       <c r="E329" t="str">
-        <v>19800613-0036</v>
+        <v>19800613-9805</v>
       </c>
       <c r="F329" t="str">
         <v>26/8 2026</v>
@@ -8704,7 +8704,7 @@
         <v>Nadia Danielsson</v>
       </c>
       <c r="E330" t="str">
-        <v>19800613-0036</v>
+        <v>19800613-9805</v>
       </c>
       <c r="F330" t="str">
         <v>28/8 2026</v>
@@ -8730,7 +8730,7 @@
         <v>Nadia Danielsson</v>
       </c>
       <c r="E331" t="str">
-        <v>19800613-0036</v>
+        <v>19800613-9805</v>
       </c>
       <c r="F331" s="1">
         <v>46264</v>
@@ -8756,7 +8756,7 @@
         <v>Nadia Danielsson</v>
       </c>
       <c r="E332" t="str">
-        <v>19800613-0036</v>
+        <v>19800613-9805</v>
       </c>
       <c r="F332" s="1">
         <v>46265</v>
@@ -8782,7 +8782,7 @@
         <v>Daniel Hassan</v>
       </c>
       <c r="E333" t="str">
-        <v>19671217-0536</v>
+        <v>19671217-9818</v>
       </c>
       <c r="F333" s="1">
         <v>46247</v>
@@ -8808,7 +8808,7 @@
         <v>Daniel Hassan</v>
       </c>
       <c r="E334" t="str">
-        <v>19671217-0536</v>
+        <v>19671217-9818</v>
       </c>
       <c r="F334" s="1">
         <v>46249</v>
@@ -8834,7 +8834,7 @@
         <v>Daniel Hassan</v>
       </c>
       <c r="E335" t="str">
-        <v>19671217-0536</v>
+        <v>19671217-9818</v>
       </c>
       <c r="F335" s="1">
         <v>46259</v>
@@ -8860,7 +8860,7 @@
         <v>Daniel Hassan</v>
       </c>
       <c r="E336" t="str">
-        <v>19671217-0536</v>
+        <v>19671217-9818</v>
       </c>
       <c r="F336" t="str">
         <v>2026-08-26</v>
@@ -8886,7 +8886,7 @@
         <v>Daniel Hassan</v>
       </c>
       <c r="E337" t="str">
-        <v>19671217-0536</v>
+        <v>19671217-9818</v>
       </c>
       <c r="F337" s="1">
         <v>46265</v>
@@ -8912,7 +8912,7 @@
         <v>Yusuf Mattsson</v>
       </c>
       <c r="E338" t="str">
-        <v>20001221-4953</v>
+        <v>20001221-9895</v>
       </c>
       <c r="F338" s="1">
         <v>46239</v>
@@ -8938,7 +8938,7 @@
         <v>Yusuf Mattsson</v>
       </c>
       <c r="E339" t="str">
-        <v>20001221-4953</v>
+        <v>20001221-9895</v>
       </c>
       <c r="F339" s="1">
         <v>46242</v>
@@ -8964,7 +8964,7 @@
         <v>Yusuf Mattsson</v>
       </c>
       <c r="E340" t="str">
-        <v>20001221-4953</v>
+        <v>20001221-9895</v>
       </c>
       <c r="F340" s="1">
         <v>46246</v>
@@ -8990,7 +8990,7 @@
         <v>Yusuf Mattsson</v>
       </c>
       <c r="E341" t="str">
-        <v>20001221-4953</v>
+        <v>20001221-9895</v>
       </c>
       <c r="F341" s="1">
         <v>46249</v>
@@ -9016,7 +9016,7 @@
         <v>Yusuf Mattsson</v>
       </c>
       <c r="E342" t="str">
-        <v>20001221-4953</v>
+        <v>20001221-9895</v>
       </c>
       <c r="F342" s="1">
         <v>46255</v>
@@ -9042,7 +9042,7 @@
         <v>Yusuf Mattsson</v>
       </c>
       <c r="E343" t="str">
-        <v>20001221-4953</v>
+        <v>20001221-9895</v>
       </c>
       <c r="F343" t="str">
         <v>27/8 2026</v>
@@ -9068,7 +9068,7 @@
         <v>Yusuf Mattsson</v>
       </c>
       <c r="E344" t="str">
-        <v>20001221-4953</v>
+        <v>20001221-9895</v>
       </c>
       <c r="F344" t="str">
         <v>29/8 2026</v>
@@ -9094,7 +9094,7 @@
         <v>Ali Mohamed</v>
       </c>
       <c r="E345" t="str">
-        <v>19700223-1483</v>
+        <v>19700223-9825</v>
       </c>
       <c r="F345" s="1">
         <v>46240</v>
@@ -9120,7 +9120,7 @@
         <v>Ali Mohamed</v>
       </c>
       <c r="E346" t="str">
-        <v>19700223-1483</v>
+        <v>19700223-9825</v>
       </c>
       <c r="F346" s="1">
         <v>46253</v>
@@ -9146,7 +9146,7 @@
         <v>Ali Mohamed</v>
       </c>
       <c r="E347" t="str">
-        <v>19700223-1483</v>
+        <v>19700223-9825</v>
       </c>
       <c r="F347" s="1">
         <v>46256</v>
@@ -9172,7 +9172,7 @@
         <v>Ali Mohamed</v>
       </c>
       <c r="E348" t="str">
-        <v>19700223-1483</v>
+        <v>19700223-9825</v>
       </c>
       <c r="F348" s="1">
         <v>46259</v>
@@ -9198,7 +9198,7 @@
         <v>Maja Olsson</v>
       </c>
       <c r="E349" t="str">
-        <v>19901103-4783</v>
+        <v>19901103-9899</v>
       </c>
       <c r="F349" s="1">
         <v>46257</v>
@@ -9224,7 +9224,7 @@
         <v>Maja Olsson</v>
       </c>
       <c r="E350" t="str">
-        <v>19901103-4783</v>
+        <v>19901103-9899</v>
       </c>
       <c r="F350" s="1">
         <v>46258</v>
@@ -9250,7 +9250,7 @@
         <v>Freja Wallin</v>
       </c>
       <c r="E351" t="str">
-        <v>19690921-5946</v>
+        <v>19690921-9914</v>
       </c>
       <c r="F351" s="1">
         <v>46237</v>
@@ -9276,7 +9276,7 @@
         <v>Freja Wallin</v>
       </c>
       <c r="E352" t="str">
-        <v>19690921-5946</v>
+        <v>19690921-9914</v>
       </c>
       <c r="F352" s="1">
         <v>46240</v>
@@ -9302,7 +9302,7 @@
         <v>Freja Wallin</v>
       </c>
       <c r="E353" t="str">
-        <v>19690921-5946</v>
+        <v>19690921-9914</v>
       </c>
       <c r="F353" s="1">
         <v>46241</v>
@@ -9328,7 +9328,7 @@
         <v>Freja Wallin</v>
       </c>
       <c r="E354" t="str">
-        <v>19690921-5946</v>
+        <v>19690921-9914</v>
       </c>
       <c r="F354" s="1">
         <v>46249</v>
@@ -9354,7 +9354,7 @@
         <v>Freja Wallin</v>
       </c>
       <c r="E355" t="str">
-        <v>19690921-5946</v>
+        <v>19690921-9914</v>
       </c>
       <c r="F355" s="1">
         <v>46251</v>
@@ -9380,7 +9380,7 @@
         <v>Freja Wallin</v>
       </c>
       <c r="E356" t="str">
-        <v>19690921-5946</v>
+        <v>19690921-9914</v>
       </c>
       <c r="F356" s="1">
         <v>46253</v>
@@ -9406,7 +9406,7 @@
         <v>Freja Wallin</v>
       </c>
       <c r="E357" t="str">
-        <v>19690921-5946</v>
+        <v>19690921-9914</v>
       </c>
       <c r="F357" s="1">
         <v>46260</v>
@@ -9452,7 +9452,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="E360" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="F360" s="1">
         <v>46236</v>
@@ -9478,7 +9478,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="E361" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="F361" t="str">
         <v>3/8 2026</v>
@@ -9504,7 +9504,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="E362" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="F362" t="str">
         <v>2026-08-07</v>
@@ -9530,7 +9530,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="E363" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="F363" t="str">
         <v>8/8 2026</v>
@@ -9556,7 +9556,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="E364" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="F364" s="1">
         <v>46244</v>
@@ -9582,7 +9582,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="E365" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="F365" t="str">
         <v>12/8 2026</v>
@@ -9608,7 +9608,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="E366" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="F366" t="str">
         <v>18/8 2026</v>
@@ -9634,7 +9634,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="E367" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="F367" s="1">
         <v>46254</v>
@@ -9660,7 +9660,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="E368" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="F368" s="1">
         <v>46256</v>
@@ -9686,7 +9686,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="E369" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="F369" s="1">
         <v>46258</v>
@@ -9712,7 +9712,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="E370" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="F370" s="1">
         <v>46259</v>
@@ -9738,7 +9738,7 @@
         <v>Jonas Axelsson</v>
       </c>
       <c r="E371" t="str">
-        <v>19711208-7296</v>
+        <v>19711208-9946</v>
       </c>
       <c r="F371" t="str">
         <v>2026-08-31</v>
@@ -9764,7 +9764,7 @@
         <v>Yasmin Axelsson</v>
       </c>
       <c r="E372" t="str">
-        <v>19731214-2289</v>
+        <v>19731214-9847</v>
       </c>
       <c r="F372" s="1">
         <v>46236</v>
@@ -9790,7 +9790,7 @@
         <v>Yasmin Axelsson</v>
       </c>
       <c r="E373" t="str">
-        <v>19731214-2289</v>
+        <v>19731214-9847</v>
       </c>
       <c r="F373" s="1">
         <v>46237</v>
@@ -9816,7 +9816,7 @@
         <v>Yasmin Axelsson</v>
       </c>
       <c r="E374" t="str">
-        <v>19731214-2289</v>
+        <v>19731214-9847</v>
       </c>
       <c r="F374" s="1">
         <v>46238</v>
@@ -9842,7 +9842,7 @@
         <v>Yasmin Axelsson</v>
       </c>
       <c r="E375" t="str">
-        <v>19731214-2289</v>
+        <v>19731214-9847</v>
       </c>
       <c r="F375" t="str">
         <v>9/8 2026</v>
@@ -9868,7 +9868,7 @@
         <v>Yasmin Axelsson</v>
       </c>
       <c r="E376" t="str">
-        <v>19731214-2289</v>
+        <v>19731214-9847</v>
       </c>
       <c r="F376" s="1">
         <v>46245</v>
@@ -9894,7 +9894,7 @@
         <v>Yasmin Axelsson</v>
       </c>
       <c r="E377" t="str">
-        <v>19731214-2289</v>
+        <v>19731214-9847</v>
       </c>
       <c r="F377" s="1">
         <v>46251</v>
@@ -9920,7 +9920,7 @@
         <v>Yasmin Axelsson</v>
       </c>
       <c r="E378" t="str">
-        <v>19731214-2289</v>
+        <v>19731214-9847</v>
       </c>
       <c r="F378" t="str">
         <v>19/8 2026</v>
@@ -9946,7 +9946,7 @@
         <v>Yasmin Axelsson</v>
       </c>
       <c r="E379" t="str">
-        <v>19731214-2289</v>
+        <v>19731214-9847</v>
       </c>
       <c r="F379" t="str">
         <v>2026-08-28</v>
@@ -9972,7 +9972,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="E380" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="F380" s="1">
         <v>46237</v>
@@ -9998,7 +9998,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="E381" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="F381" s="1">
         <v>46239</v>
@@ -10024,7 +10024,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="E382" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="F382" s="1">
         <v>46245</v>
@@ -10050,7 +10050,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="E383" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="F383" s="1">
         <v>46249</v>
@@ -10076,7 +10076,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="E384" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="F384" t="str">
         <v>2026-08-19</v>
@@ -10102,7 +10102,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="E385" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="F385" t="str">
         <v>2026-08-25</v>
@@ -10128,7 +10128,7 @@
         <v>Anna Jansson</v>
       </c>
       <c r="E386" t="str">
-        <v>20040924-8952</v>
+        <v>20040924-9976</v>
       </c>
       <c r="F386" s="1">
         <v>46263</v>
@@ -10154,7 +10154,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="E387" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="F387" t="str">
         <v>2026-08-05</v>
@@ -10180,7 +10180,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="E388" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="F388" s="1">
         <v>46240</v>
@@ -10206,7 +10206,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="E389" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="F389" s="1">
         <v>46247</v>
@@ -10232,7 +10232,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="E390" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="F390" s="1">
         <v>46256</v>
@@ -10258,7 +10258,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="E391" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="F391" t="str">
         <v>2026-08-26</v>
@@ -10284,7 +10284,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="E392" t="str">
-        <v>19830317-3671</v>
+        <v>19830317-9876</v>
       </c>
       <c r="F392" s="1">
         <v>46261</v>
@@ -10310,7 +10310,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="E393" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="F393" t="str">
         <v>2026-08-05</v>
@@ -10336,7 +10336,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="E394" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="F394" s="1">
         <v>46240</v>
@@ -10362,7 +10362,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="E395" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="F395" s="1">
         <v>46241</v>
@@ -10388,7 +10388,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="E396" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="F396" s="1">
         <v>46242</v>
@@ -10414,7 +10414,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="E397" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="F397" s="1">
         <v>46244</v>
@@ -10440,7 +10440,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="E398" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="F398" s="1">
         <v>46246</v>
@@ -10466,7 +10466,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="E399" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="F399" s="1">
         <v>46247</v>
@@ -10492,7 +10492,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="E400" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="F400" s="1">
         <v>46256</v>
@@ -10518,7 +10518,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="E401" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="F401" s="1">
         <v>46259</v>
@@ -10544,7 +10544,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="E402" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="F402" s="1">
         <v>46260</v>
@@ -10570,7 +10570,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="E403" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="F403" s="1">
         <v>46262</v>
@@ -10596,7 +10596,7 @@
         <v>Isak Svensson</v>
       </c>
       <c r="E404" t="str">
-        <v>20040904-6208</v>
+        <v>20040904-9921</v>
       </c>
       <c r="F404" s="1">
         <v>46265</v>
@@ -10642,7 +10642,7 @@
         <v>Viktor Forsberg</v>
       </c>
       <c r="E407" t="str">
-        <v>19720108-9765</v>
+        <v>19720108-9997</v>
       </c>
       <c r="F407" s="1">
         <v>46239</v>
@@ -10668,7 +10668,7 @@
         <v>Viktor Forsberg</v>
       </c>
       <c r="E408" t="str">
-        <v>19720108-9765</v>
+        <v>19720108-9997</v>
       </c>
       <c r="F408" s="1">
         <v>46242</v>
@@ -10694,7 +10694,7 @@
         <v>Viktor Forsberg</v>
       </c>
       <c r="E409" t="str">
-        <v>19720108-9765</v>
+        <v>19720108-9997</v>
       </c>
       <c r="F409" s="1">
         <v>46253</v>
@@ -10720,7 +10720,7 @@
         <v>Viktor Forsberg</v>
       </c>
       <c r="E410" t="str">
-        <v>19720108-9765</v>
+        <v>19720108-9997</v>
       </c>
       <c r="F410" t="str">
         <v>25/8 2026</v>
@@ -10746,7 +10746,7 @@
         <v>Viktor Forsberg</v>
       </c>
       <c r="E411" t="str">
-        <v>19720108-9765</v>
+        <v>19720108-9997</v>
       </c>
       <c r="F411" s="1">
         <v>46260</v>
@@ -10772,7 +10772,7 @@
         <v>Viktor Forsberg</v>
       </c>
       <c r="E412" t="str">
-        <v>19720108-9765</v>
+        <v>19720108-9997</v>
       </c>
       <c r="F412" s="1">
         <v>46261</v>
@@ -10798,7 +10798,7 @@
         <v>Jakob Jonsson</v>
       </c>
       <c r="E413" t="str">
-        <v>19770823-3841</v>
+        <v>19770823-9871</v>
       </c>
       <c r="F413" t="str">
         <v>2026-08-05</v>
@@ -10824,7 +10824,7 @@
         <v>Jakob Jonsson</v>
       </c>
       <c r="E414" t="str">
-        <v>19770823-3841</v>
+        <v>19770823-9871</v>
       </c>
       <c r="F414" s="1">
         <v>46240</v>
@@ -10850,7 +10850,7 @@
         <v>Jakob Jonsson</v>
       </c>
       <c r="E415" t="str">
-        <v>19770823-3841</v>
+        <v>19770823-9871</v>
       </c>
       <c r="F415" s="1">
         <v>46242</v>
@@ -10876,7 +10876,7 @@
         <v>Jakob Jonsson</v>
       </c>
       <c r="E416" t="str">
-        <v>19770823-3841</v>
+        <v>19770823-9871</v>
       </c>
       <c r="F416" s="1">
         <v>46244</v>
@@ -10902,7 +10902,7 @@
         <v>Jakob Jonsson</v>
       </c>
       <c r="E417" t="str">
-        <v>19770823-3841</v>
+        <v>19770823-9871</v>
       </c>
       <c r="F417" s="1">
         <v>46245</v>
@@ -10928,7 +10928,7 @@
         <v>Jakob Jonsson</v>
       </c>
       <c r="E418" t="str">
-        <v>19770823-3841</v>
+        <v>19770823-9871</v>
       </c>
       <c r="F418" s="1">
         <v>46246</v>
@@ -10954,7 +10954,7 @@
         <v>Jakob Jonsson</v>
       </c>
       <c r="E419" t="str">
-        <v>19770823-3841</v>
+        <v>19770823-9871</v>
       </c>
       <c r="F419" t="str">
         <v>18/8 2026</v>
@@ -10980,7 +10980,7 @@
         <v>Jakob Jonsson</v>
       </c>
       <c r="E420" t="str">
-        <v>19770823-3841</v>
+        <v>19770823-9871</v>
       </c>
       <c r="F420" s="1">
         <v>46254</v>
@@ -11006,7 +11006,7 @@
         <v>Jakob Jonsson</v>
       </c>
       <c r="E421" t="str">
-        <v>19770823-3841</v>
+        <v>19770823-9871</v>
       </c>
       <c r="F421" t="str">
         <v>2026-08-21</v>
@@ -11032,7 +11032,7 @@
         <v>Jakob Jonsson</v>
       </c>
       <c r="E422" t="str">
-        <v>19770823-3841</v>
+        <v>19770823-9871</v>
       </c>
       <c r="F422" s="1">
         <v>46257</v>
@@ -11058,7 +11058,7 @@
         <v>Jakob Jonsson</v>
       </c>
       <c r="E423" t="str">
-        <v>19770823-3841</v>
+        <v>19770823-9871</v>
       </c>
       <c r="F423" s="1">
         <v>46263</v>
@@ -11084,7 +11084,7 @@
         <v>Jakob Jonsson</v>
       </c>
       <c r="E424" t="str">
-        <v>19770823-3841</v>
+        <v>19770823-9871</v>
       </c>
       <c r="F424" s="1">
         <v>46265</v>
@@ -11110,7 +11110,7 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="E425" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="F425" s="1">
         <v>46236</v>
@@ -11136,7 +11136,7 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="E426" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="F426" s="1">
         <v>46238</v>
@@ -11162,7 +11162,7 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="E427" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="F427" s="1">
         <v>46250</v>
@@ -11188,7 +11188,7 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="E428" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="F428" s="1">
         <v>46252</v>
@@ -11214,7 +11214,7 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="E429" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="F429" s="1">
         <v>46255</v>
@@ -11240,7 +11240,7 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="E430" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="F430" s="1">
         <v>46258</v>
@@ -11266,7 +11266,7 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="E431" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="F431" t="str">
         <v>26/8 2026</v>
@@ -11292,7 +11292,7 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="E432" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="F432" t="str">
         <v>29/8 2026</v>
@@ -11318,7 +11318,7 @@
         <v>Yusuf Olsson</v>
       </c>
       <c r="E433" t="str">
-        <v>19860920-8924</v>
+        <v>19860920-9971</v>
       </c>
       <c r="F433" s="1">
         <v>46264</v>
